--- a/resultados/uniaodavitoria/erros_varredura.xlsx
+++ b/resultados/uniaodavitoria/erros_varredura.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br/</t>
+          <t>https://uniaodavitoria.pr.gov.br/concurso-pss/bolsa-de-estudos-2026/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-04 00:42:51</t>
+          <t>2026-08-04 00:53:33</t>
         </is>
       </c>
     </row>
@@ -484,23 +484,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br</t>
+          <t>https://uniaodavitoria.pr.gov.br/concurso-pss/bolsa-de-estudos-2026/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>404</v>
       </c>
       <c r="E3" t="n">
         <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-04 00:52:29</t>
+          <t>2026-08-04 00:53:51</t>
         </is>
       </c>
     </row>
@@ -512,23 +512,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://uniaodavitoria.pr.gov.br/concurso-pss/bolsa-de-estudos-2026/</t>
+          <t>http://www.uniaodavitoria.pr.gov.br/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-04 00:53:33</t>
+          <t>2026-08-04 00:57:23</t>
         </is>
       </c>
     </row>
@@ -540,23 +540,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://uniaodavitoria.pr.gov.br/concurso-pss/bolsa-de-estudos-2026/</t>
+          <t>http://www.uniaodavitoria.pr.gov.br/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTTP_404</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-04 00:53:51</t>
+          <t>2026-08-04 00:57:24</t>
         </is>
       </c>
     </row>
@@ -568,12 +568,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br/conferenciadascidades</t>
+          <t>http://www.uniaodavitoria.pr.gov.br</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -584,7 +584,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-04 00:54:03</t>
+          <t>2026-08-04 00:57:36</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br/</t>
+          <t>http://www.uniaodavitoria.pr.gov.br</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-04 00:57:23</t>
+          <t>2026-08-04 00:57:37</t>
         </is>
       </c>
     </row>
@@ -624,23 +624,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br/</t>
+          <t>http://www.uniaodavitoria.pr.gov.br/conferenciadascidades</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-04 00:57:24</t>
+          <t>2026-08-04 00:57:49</t>
         </is>
       </c>
     </row>
@@ -652,12 +652,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br</t>
+          <t>http://www.uniaodavitoria.pr.gov.br/conferenciadascidades</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -668,7 +668,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-04 00:57:36</t>
+          <t>2026-08-04 00:57:50</t>
         </is>
       </c>
     </row>
@@ -680,23 +680,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br</t>
+          <t>http://www.uniaodavitoria.pr.gov.br/</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SELENIUM_ERRO: WebDriverException</t>
+          <t>TIMEOUT_OU_CONEXAO</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-04 00:57:37</t>
+          <t>2026-08-04 21:22:55</t>
         </is>
       </c>
     </row>
@@ -708,23 +708,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>http://www.uniaodavitoria.pr.gov.br/conferenciadascidades</t>
+          <t>http://www.uniaodavitoria.pr.gov.br/</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TIMEOUT_OU_CONEXAO</t>
+          <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-04 00:57:49</t>
+          <t>2026-08-04 21:22:58</t>
         </is>
       </c>
     </row>
@@ -736,23 +736,107 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>http://www.uniaodavitoria.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-04 21:23:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>uniaodavitoria</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>http://www.uniaodavitoria.pr.gov.br</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-04 21:23:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>uniaodavitoria</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>http://www.uniaodavitoria.pr.gov.br/conferenciadascidades</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-04 21:23:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>uniaodavitoria</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>http://www.uniaodavitoria.pr.gov.br/conferenciadascidades</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>SELENIUM_ERRO: WebDriverException</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-04 00:57:50</t>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-04 21:23:29</t>
         </is>
       </c>
     </row>
